--- a/src/data/COREP_files/G_EU_C_C2200.xlsx
+++ b/src/data/COREP_files/G_EU_C_C2200.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S65"/>
+  <dimension ref="A1:S57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1"/>
@@ -581,6 +581,33 @@
           <t>TOTAL POSITIONS IN NON-REPORTING CURRENCIES</t>
         </is>
       </c>
+      <c r="G9" t="n">
+        <v>4</v>
+      </c>
+      <c r="H9" t="n">
+        <v>5</v>
+      </c>
+      <c r="I9" t="n">
+        <v>6</v>
+      </c>
+      <c r="J9" t="n">
+        <v>7</v>
+      </c>
+      <c r="K9" t="n">
+        <v>8</v>
+      </c>
+      <c r="L9" t="n">
+        <v>9</v>
+      </c>
+      <c r="M9" t="n">
+        <v>10</v>
+      </c>
+      <c r="N9" t="n">
+        <v>11</v>
+      </c>
+      <c r="R9" t="n">
+        <v>12</v>
+      </c>
       <c r="S9" t="inlineStr">
         <is>
           <t>Cell linked to CA</t>
@@ -598,6 +625,33 @@
           <t>Currencies closely correlated</t>
         </is>
       </c>
+      <c r="G10" t="n">
+        <v>5</v>
+      </c>
+      <c r="H10" t="n">
+        <v>6</v>
+      </c>
+      <c r="I10" t="n">
+        <v>7</v>
+      </c>
+      <c r="J10" t="n">
+        <v>8</v>
+      </c>
+      <c r="K10" t="n">
+        <v>9</v>
+      </c>
+      <c r="L10" t="n">
+        <v>10</v>
+      </c>
+      <c r="M10" t="n">
+        <v>11</v>
+      </c>
+      <c r="N10" t="n">
+        <v>12</v>
+      </c>
+      <c r="R10" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="11">
       <c r="B11" t="inlineStr">
@@ -610,12 +664,39 @@
           <t>All other currencies (including CIUs treated as different currencies)</t>
         </is>
       </c>
+      <c r="G11" t="n">
+        <v>6</v>
+      </c>
+      <c r="H11" t="n">
+        <v>7</v>
+      </c>
+      <c r="I11" t="n">
+        <v>8</v>
+      </c>
+      <c r="J11" t="n">
+        <v>9</v>
+      </c>
+      <c r="K11" t="n">
+        <v>10</v>
+      </c>
+      <c r="L11" t="n">
+        <v>11</v>
+      </c>
+      <c r="M11" t="n">
+        <v>12</v>
+      </c>
+      <c r="N11" t="n">
+        <v>13</v>
+      </c>
       <c r="O11" t="n">
         <v>8</v>
       </c>
       <c r="P11" t="n">
         <v>8</v>
       </c>
+      <c r="R11" t="n">
+        <v>14</v>
+      </c>
     </row>
     <row r="12">
       <c r="B12" t="inlineStr">
@@ -628,11 +709,38 @@
           <t xml:space="preserve">Gold </t>
         </is>
       </c>
+      <c r="G12" t="n">
+        <v>7</v>
+      </c>
+      <c r="H12" t="n">
+        <v>8</v>
+      </c>
+      <c r="I12" t="n">
+        <v>9</v>
+      </c>
+      <c r="J12" t="n">
+        <v>10</v>
+      </c>
+      <c r="K12" t="n">
+        <v>11</v>
+      </c>
+      <c r="L12" t="n">
+        <v>12</v>
+      </c>
+      <c r="M12" t="n">
+        <v>13</v>
+      </c>
+      <c r="N12" t="n">
+        <v>14</v>
+      </c>
       <c r="O12" t="n">
         <v>8</v>
       </c>
       <c r="P12" t="n">
         <v>8</v>
+      </c>
+      <c r="R12" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="13">
@@ -711,6 +819,33 @@
           <t>Other assets and liabilities other than off-balance sheet items and derivatives</t>
         </is>
       </c>
+      <c r="G19" t="n">
+        <v>4</v>
+      </c>
+      <c r="H19" t="n">
+        <v>5</v>
+      </c>
+      <c r="I19" t="n">
+        <v>6</v>
+      </c>
+      <c r="J19" t="n">
+        <v>7</v>
+      </c>
+      <c r="K19" t="n">
+        <v>8</v>
+      </c>
+      <c r="L19" t="n">
+        <v>9</v>
+      </c>
+      <c r="M19" t="n">
+        <v>10</v>
+      </c>
+      <c r="N19" t="n">
+        <v>11</v>
+      </c>
+      <c r="R19" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="20">
       <c r="B20" t="n">
@@ -753,6 +888,30 @@
           <t>EUR</t>
         </is>
       </c>
+      <c r="H23" t="n">
+        <v>8</v>
+      </c>
+      <c r="I23" t="n">
+        <v>9</v>
+      </c>
+      <c r="J23" t="n">
+        <v>10</v>
+      </c>
+      <c r="K23" t="n">
+        <v>11</v>
+      </c>
+      <c r="L23" t="n">
+        <v>12</v>
+      </c>
+      <c r="M23" t="n">
+        <v>13</v>
+      </c>
+      <c r="N23" t="n">
+        <v>14</v>
+      </c>
+      <c r="R23" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="24">
       <c r="B24" t="n">
@@ -768,6 +927,30 @@
           <t>ALL</t>
         </is>
       </c>
+      <c r="H24" t="n">
+        <v>9</v>
+      </c>
+      <c r="I24" t="n">
+        <v>10</v>
+      </c>
+      <c r="J24" t="n">
+        <v>11</v>
+      </c>
+      <c r="K24" t="n">
+        <v>12</v>
+      </c>
+      <c r="L24" t="n">
+        <v>13</v>
+      </c>
+      <c r="M24" t="n">
+        <v>14</v>
+      </c>
+      <c r="N24" t="n">
+        <v>15</v>
+      </c>
+      <c r="R24" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="25">
       <c r="B25" t="n">
@@ -783,6 +966,30 @@
           <t>ARS</t>
         </is>
       </c>
+      <c r="H25" t="n">
+        <v>10</v>
+      </c>
+      <c r="I25" t="n">
+        <v>11</v>
+      </c>
+      <c r="J25" t="n">
+        <v>12</v>
+      </c>
+      <c r="K25" t="n">
+        <v>13</v>
+      </c>
+      <c r="L25" t="n">
+        <v>14</v>
+      </c>
+      <c r="M25" t="n">
+        <v>15</v>
+      </c>
+      <c r="N25" t="n">
+        <v>16</v>
+      </c>
+      <c r="R25" t="n">
+        <v>17</v>
+      </c>
     </row>
     <row r="26">
       <c r="B26" t="n">
@@ -798,6 +1005,30 @@
           <t>AUD</t>
         </is>
       </c>
+      <c r="H26" t="n">
+        <v>11</v>
+      </c>
+      <c r="I26" t="n">
+        <v>12</v>
+      </c>
+      <c r="J26" t="n">
+        <v>13</v>
+      </c>
+      <c r="K26" t="n">
+        <v>14</v>
+      </c>
+      <c r="L26" t="n">
+        <v>15</v>
+      </c>
+      <c r="M26" t="n">
+        <v>16</v>
+      </c>
+      <c r="N26" t="n">
+        <v>17</v>
+      </c>
+      <c r="R26" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="27">
       <c r="B27" t="n">
@@ -813,6 +1044,30 @@
           <t>BRL</t>
         </is>
       </c>
+      <c r="H27" t="n">
+        <v>12</v>
+      </c>
+      <c r="I27" t="n">
+        <v>13</v>
+      </c>
+      <c r="J27" t="n">
+        <v>14</v>
+      </c>
+      <c r="K27" t="n">
+        <v>15</v>
+      </c>
+      <c r="L27" t="n">
+        <v>16</v>
+      </c>
+      <c r="M27" t="n">
+        <v>17</v>
+      </c>
+      <c r="N27" t="n">
+        <v>18</v>
+      </c>
+      <c r="R27" t="n">
+        <v>19</v>
+      </c>
     </row>
     <row r="28">
       <c r="B28" t="n">
@@ -828,6 +1083,30 @@
           <t>BGN</t>
         </is>
       </c>
+      <c r="H28" t="n">
+        <v>13</v>
+      </c>
+      <c r="I28" t="n">
+        <v>14</v>
+      </c>
+      <c r="J28" t="n">
+        <v>15</v>
+      </c>
+      <c r="K28" t="n">
+        <v>16</v>
+      </c>
+      <c r="L28" t="n">
+        <v>17</v>
+      </c>
+      <c r="M28" t="n">
+        <v>18</v>
+      </c>
+      <c r="N28" t="n">
+        <v>19</v>
+      </c>
+      <c r="R28" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="29">
       <c r="B29" t="n">
@@ -843,6 +1122,30 @@
           <t>CAD</t>
         </is>
       </c>
+      <c r="H29" t="n">
+        <v>14</v>
+      </c>
+      <c r="I29" t="n">
+        <v>15</v>
+      </c>
+      <c r="J29" t="n">
+        <v>16</v>
+      </c>
+      <c r="K29" t="n">
+        <v>17</v>
+      </c>
+      <c r="L29" t="n">
+        <v>18</v>
+      </c>
+      <c r="M29" t="n">
+        <v>19</v>
+      </c>
+      <c r="N29" t="n">
+        <v>20</v>
+      </c>
+      <c r="R29" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="30">
       <c r="B30" t="n">
@@ -858,6 +1161,30 @@
           <t>CZK</t>
         </is>
       </c>
+      <c r="H30" t="n">
+        <v>6</v>
+      </c>
+      <c r="I30" t="n">
+        <v>7</v>
+      </c>
+      <c r="J30" t="n">
+        <v>8</v>
+      </c>
+      <c r="K30" t="n">
+        <v>9</v>
+      </c>
+      <c r="L30" t="n">
+        <v>10</v>
+      </c>
+      <c r="M30" t="n">
+        <v>11</v>
+      </c>
+      <c r="N30" t="n">
+        <v>12</v>
+      </c>
+      <c r="R30" t="n">
+        <v>13</v>
+      </c>
     </row>
     <row r="31">
       <c r="B31" t="n">
@@ -873,6 +1200,30 @@
           <t>DKK</t>
         </is>
       </c>
+      <c r="H31" t="n">
+        <v>7</v>
+      </c>
+      <c r="I31" t="n">
+        <v>8</v>
+      </c>
+      <c r="J31" t="n">
+        <v>9</v>
+      </c>
+      <c r="K31" t="n">
+        <v>10</v>
+      </c>
+      <c r="L31" t="n">
+        <v>11</v>
+      </c>
+      <c r="M31" t="n">
+        <v>12</v>
+      </c>
+      <c r="N31" t="n">
+        <v>13</v>
+      </c>
+      <c r="R31" t="n">
+        <v>14</v>
+      </c>
     </row>
     <row r="32">
       <c r="B32" t="n">
@@ -888,6 +1239,30 @@
           <t>EGP</t>
         </is>
       </c>
+      <c r="H32" t="n">
+        <v>8</v>
+      </c>
+      <c r="I32" t="n">
+        <v>9</v>
+      </c>
+      <c r="J32" t="n">
+        <v>10</v>
+      </c>
+      <c r="K32" t="n">
+        <v>11</v>
+      </c>
+      <c r="L32" t="n">
+        <v>12</v>
+      </c>
+      <c r="M32" t="n">
+        <v>13</v>
+      </c>
+      <c r="N32" t="n">
+        <v>14</v>
+      </c>
+      <c r="R32" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="33">
       <c r="B33" t="n">
@@ -903,6 +1278,30 @@
           <t>GBP</t>
         </is>
       </c>
+      <c r="H33" t="n">
+        <v>9</v>
+      </c>
+      <c r="I33" t="n">
+        <v>10</v>
+      </c>
+      <c r="J33" t="n">
+        <v>11</v>
+      </c>
+      <c r="K33" t="n">
+        <v>12</v>
+      </c>
+      <c r="L33" t="n">
+        <v>13</v>
+      </c>
+      <c r="M33" t="n">
+        <v>14</v>
+      </c>
+      <c r="N33" t="n">
+        <v>15</v>
+      </c>
+      <c r="R33" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="34">
       <c r="B34" t="n">
@@ -918,6 +1317,30 @@
           <t>HUF</t>
         </is>
       </c>
+      <c r="H34" t="n">
+        <v>10</v>
+      </c>
+      <c r="I34" t="n">
+        <v>11</v>
+      </c>
+      <c r="J34" t="n">
+        <v>12</v>
+      </c>
+      <c r="K34" t="n">
+        <v>13</v>
+      </c>
+      <c r="L34" t="n">
+        <v>14</v>
+      </c>
+      <c r="M34" t="n">
+        <v>15</v>
+      </c>
+      <c r="N34" t="n">
+        <v>16</v>
+      </c>
+      <c r="R34" t="n">
+        <v>17</v>
+      </c>
     </row>
     <row r="35">
       <c r="B35" t="n">
@@ -933,6 +1356,30 @@
           <t>JPY</t>
         </is>
       </c>
+      <c r="H35" t="n">
+        <v>11</v>
+      </c>
+      <c r="I35" t="n">
+        <v>12</v>
+      </c>
+      <c r="J35" t="n">
+        <v>13</v>
+      </c>
+      <c r="K35" t="n">
+        <v>14</v>
+      </c>
+      <c r="L35" t="n">
+        <v>15</v>
+      </c>
+      <c r="M35" t="n">
+        <v>16</v>
+      </c>
+      <c r="N35" t="n">
+        <v>17</v>
+      </c>
+      <c r="R35" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="36">
       <c r="B36" t="n">
@@ -963,6 +1410,30 @@
           <t>LTL</t>
         </is>
       </c>
+      <c r="H37" t="n">
+        <v>13</v>
+      </c>
+      <c r="I37" t="n">
+        <v>14</v>
+      </c>
+      <c r="J37" t="n">
+        <v>15</v>
+      </c>
+      <c r="K37" t="n">
+        <v>16</v>
+      </c>
+      <c r="L37" t="n">
+        <v>17</v>
+      </c>
+      <c r="M37" t="n">
+        <v>18</v>
+      </c>
+      <c r="N37" t="n">
+        <v>19</v>
+      </c>
+      <c r="R37" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="38">
       <c r="B38" t="n">
@@ -978,6 +1449,30 @@
           <t>MKD</t>
         </is>
       </c>
+      <c r="H38" t="n">
+        <v>14</v>
+      </c>
+      <c r="I38" t="n">
+        <v>15</v>
+      </c>
+      <c r="J38" t="n">
+        <v>16</v>
+      </c>
+      <c r="K38" t="n">
+        <v>17</v>
+      </c>
+      <c r="L38" t="n">
+        <v>18</v>
+      </c>
+      <c r="M38" t="n">
+        <v>19</v>
+      </c>
+      <c r="N38" t="n">
+        <v>20</v>
+      </c>
+      <c r="R38" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="39">
       <c r="B39" t="n">
@@ -993,6 +1488,30 @@
           <t>MXN</t>
         </is>
       </c>
+      <c r="H39" t="n">
+        <v>15</v>
+      </c>
+      <c r="I39" t="n">
+        <v>16</v>
+      </c>
+      <c r="J39" t="n">
+        <v>17</v>
+      </c>
+      <c r="K39" t="n">
+        <v>18</v>
+      </c>
+      <c r="L39" t="n">
+        <v>19</v>
+      </c>
+      <c r="M39" t="n">
+        <v>20</v>
+      </c>
+      <c r="N39" t="n">
+        <v>21</v>
+      </c>
+      <c r="R39" t="n">
+        <v>22</v>
+      </c>
     </row>
     <row r="40">
       <c r="B40" t="n">
@@ -1008,6 +1527,30 @@
           <t>PLN</t>
         </is>
       </c>
+      <c r="H40" t="n">
+        <v>7</v>
+      </c>
+      <c r="I40" t="n">
+        <v>8</v>
+      </c>
+      <c r="J40" t="n">
+        <v>9</v>
+      </c>
+      <c r="K40" t="n">
+        <v>10</v>
+      </c>
+      <c r="L40" t="n">
+        <v>11</v>
+      </c>
+      <c r="M40" t="n">
+        <v>12</v>
+      </c>
+      <c r="N40" t="n">
+        <v>13</v>
+      </c>
+      <c r="R40" t="n">
+        <v>14</v>
+      </c>
     </row>
     <row r="41">
       <c r="B41" t="n">
@@ -1023,6 +1566,30 @@
           <t>RON</t>
         </is>
       </c>
+      <c r="H41" t="n">
+        <v>8</v>
+      </c>
+      <c r="I41" t="n">
+        <v>9</v>
+      </c>
+      <c r="J41" t="n">
+        <v>10</v>
+      </c>
+      <c r="K41" t="n">
+        <v>11</v>
+      </c>
+      <c r="L41" t="n">
+        <v>12</v>
+      </c>
+      <c r="M41" t="n">
+        <v>13</v>
+      </c>
+      <c r="N41" t="n">
+        <v>14</v>
+      </c>
+      <c r="R41" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="42">
       <c r="B42" t="n">
@@ -1038,6 +1605,30 @@
           <t>RUB</t>
         </is>
       </c>
+      <c r="H42" t="n">
+        <v>9</v>
+      </c>
+      <c r="I42" t="n">
+        <v>10</v>
+      </c>
+      <c r="J42" t="n">
+        <v>11</v>
+      </c>
+      <c r="K42" t="n">
+        <v>12</v>
+      </c>
+      <c r="L42" t="n">
+        <v>13</v>
+      </c>
+      <c r="M42" t="n">
+        <v>14</v>
+      </c>
+      <c r="N42" t="n">
+        <v>15</v>
+      </c>
+      <c r="R42" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="43">
       <c r="B43" t="n">
@@ -1053,6 +1644,30 @@
           <t>RSD</t>
         </is>
       </c>
+      <c r="H43" t="n">
+        <v>10</v>
+      </c>
+      <c r="I43" t="n">
+        <v>11</v>
+      </c>
+      <c r="J43" t="n">
+        <v>12</v>
+      </c>
+      <c r="K43" t="n">
+        <v>13</v>
+      </c>
+      <c r="L43" t="n">
+        <v>14</v>
+      </c>
+      <c r="M43" t="n">
+        <v>15</v>
+      </c>
+      <c r="N43" t="n">
+        <v>16</v>
+      </c>
+      <c r="R43" t="n">
+        <v>17</v>
+      </c>
     </row>
     <row r="44">
       <c r="B44" t="n">
@@ -1068,6 +1683,30 @@
           <t>SEK</t>
         </is>
       </c>
+      <c r="H44" t="n">
+        <v>11</v>
+      </c>
+      <c r="I44" t="n">
+        <v>12</v>
+      </c>
+      <c r="J44" t="n">
+        <v>13</v>
+      </c>
+      <c r="K44" t="n">
+        <v>14</v>
+      </c>
+      <c r="L44" t="n">
+        <v>15</v>
+      </c>
+      <c r="M44" t="n">
+        <v>16</v>
+      </c>
+      <c r="N44" t="n">
+        <v>17</v>
+      </c>
+      <c r="R44" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="45">
       <c r="B45" t="n">
@@ -1083,6 +1722,30 @@
           <t>CHF</t>
         </is>
       </c>
+      <c r="H45" t="n">
+        <v>12</v>
+      </c>
+      <c r="I45" t="n">
+        <v>13</v>
+      </c>
+      <c r="J45" t="n">
+        <v>14</v>
+      </c>
+      <c r="K45" t="n">
+        <v>15</v>
+      </c>
+      <c r="L45" t="n">
+        <v>16</v>
+      </c>
+      <c r="M45" t="n">
+        <v>17</v>
+      </c>
+      <c r="N45" t="n">
+        <v>18</v>
+      </c>
+      <c r="R45" t="n">
+        <v>19</v>
+      </c>
     </row>
     <row r="46">
       <c r="B46" t="n">
@@ -1098,6 +1761,30 @@
           <t>TRY</t>
         </is>
       </c>
+      <c r="H46" t="n">
+        <v>13</v>
+      </c>
+      <c r="I46" t="n">
+        <v>14</v>
+      </c>
+      <c r="J46" t="n">
+        <v>15</v>
+      </c>
+      <c r="K46" t="n">
+        <v>16</v>
+      </c>
+      <c r="L46" t="n">
+        <v>17</v>
+      </c>
+      <c r="M46" t="n">
+        <v>18</v>
+      </c>
+      <c r="N46" t="n">
+        <v>19</v>
+      </c>
+      <c r="R46" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="47">
       <c r="B47" t="n">
@@ -1113,6 +1800,30 @@
           <t>UAH</t>
         </is>
       </c>
+      <c r="H47" t="n">
+        <v>14</v>
+      </c>
+      <c r="I47" t="n">
+        <v>15</v>
+      </c>
+      <c r="J47" t="n">
+        <v>16</v>
+      </c>
+      <c r="K47" t="n">
+        <v>17</v>
+      </c>
+      <c r="L47" t="n">
+        <v>18</v>
+      </c>
+      <c r="M47" t="n">
+        <v>19</v>
+      </c>
+      <c r="N47" t="n">
+        <v>20</v>
+      </c>
+      <c r="R47" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="48">
       <c r="B48" t="n">
@@ -1128,6 +1839,30 @@
           <t>USD</t>
         </is>
       </c>
+      <c r="H48" t="n">
+        <v>15</v>
+      </c>
+      <c r="I48" t="n">
+        <v>16</v>
+      </c>
+      <c r="J48" t="n">
+        <v>17</v>
+      </c>
+      <c r="K48" t="n">
+        <v>18</v>
+      </c>
+      <c r="L48" t="n">
+        <v>19</v>
+      </c>
+      <c r="M48" t="n">
+        <v>20</v>
+      </c>
+      <c r="N48" t="n">
+        <v>21</v>
+      </c>
+      <c r="R48" t="n">
+        <v>22</v>
+      </c>
     </row>
     <row r="49">
       <c r="B49" t="n">
@@ -1143,6 +1878,30 @@
           <t>ISK</t>
         </is>
       </c>
+      <c r="H49" t="n">
+        <v>16</v>
+      </c>
+      <c r="I49" t="n">
+        <v>17</v>
+      </c>
+      <c r="J49" t="n">
+        <v>18</v>
+      </c>
+      <c r="K49" t="n">
+        <v>19</v>
+      </c>
+      <c r="L49" t="n">
+        <v>20</v>
+      </c>
+      <c r="M49" t="n">
+        <v>21</v>
+      </c>
+      <c r="N49" t="n">
+        <v>22</v>
+      </c>
+      <c r="R49" t="n">
+        <v>23</v>
+      </c>
     </row>
     <row r="50">
       <c r="B50" t="n">
@@ -1158,6 +1917,30 @@
           <t>NOK</t>
         </is>
       </c>
+      <c r="H50" t="n">
+        <v>8</v>
+      </c>
+      <c r="I50" t="n">
+        <v>9</v>
+      </c>
+      <c r="J50" t="n">
+        <v>10</v>
+      </c>
+      <c r="K50" t="n">
+        <v>11</v>
+      </c>
+      <c r="L50" t="n">
+        <v>12</v>
+      </c>
+      <c r="M50" t="n">
+        <v>13</v>
+      </c>
+      <c r="N50" t="n">
+        <v>14</v>
+      </c>
+      <c r="R50" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="51">
       <c r="B51" t="inlineStr">
@@ -1175,6 +1958,30 @@
           <t>HKD</t>
         </is>
       </c>
+      <c r="H51" t="n">
+        <v>9</v>
+      </c>
+      <c r="I51" t="n">
+        <v>10</v>
+      </c>
+      <c r="J51" t="n">
+        <v>11</v>
+      </c>
+      <c r="K51" t="n">
+        <v>12</v>
+      </c>
+      <c r="L51" t="n">
+        <v>13</v>
+      </c>
+      <c r="M51" t="n">
+        <v>14</v>
+      </c>
+      <c r="N51" t="n">
+        <v>15</v>
+      </c>
+      <c r="R51" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="52">
       <c r="B52" t="inlineStr">
@@ -1192,6 +1999,30 @@
           <t>TWD</t>
         </is>
       </c>
+      <c r="H52" t="n">
+        <v>10</v>
+      </c>
+      <c r="I52" t="n">
+        <v>11</v>
+      </c>
+      <c r="J52" t="n">
+        <v>12</v>
+      </c>
+      <c r="K52" t="n">
+        <v>13</v>
+      </c>
+      <c r="L52" t="n">
+        <v>14</v>
+      </c>
+      <c r="M52" t="n">
+        <v>15</v>
+      </c>
+      <c r="N52" t="n">
+        <v>16</v>
+      </c>
+      <c r="R52" t="n">
+        <v>17</v>
+      </c>
     </row>
     <row r="53">
       <c r="B53" t="inlineStr">
@@ -1209,6 +2040,30 @@
           <t>NZD</t>
         </is>
       </c>
+      <c r="H53" t="n">
+        <v>11</v>
+      </c>
+      <c r="I53" t="n">
+        <v>12</v>
+      </c>
+      <c r="J53" t="n">
+        <v>13</v>
+      </c>
+      <c r="K53" t="n">
+        <v>14</v>
+      </c>
+      <c r="L53" t="n">
+        <v>15</v>
+      </c>
+      <c r="M53" t="n">
+        <v>16</v>
+      </c>
+      <c r="N53" t="n">
+        <v>17</v>
+      </c>
+      <c r="R53" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="54">
       <c r="B54" t="inlineStr">
@@ -1226,6 +2081,30 @@
           <t>SGD</t>
         </is>
       </c>
+      <c r="H54" t="n">
+        <v>12</v>
+      </c>
+      <c r="I54" t="n">
+        <v>13</v>
+      </c>
+      <c r="J54" t="n">
+        <v>14</v>
+      </c>
+      <c r="K54" t="n">
+        <v>15</v>
+      </c>
+      <c r="L54" t="n">
+        <v>16</v>
+      </c>
+      <c r="M54" t="n">
+        <v>17</v>
+      </c>
+      <c r="N54" t="n">
+        <v>18</v>
+      </c>
+      <c r="R54" t="n">
+        <v>19</v>
+      </c>
     </row>
     <row r="55">
       <c r="B55" t="inlineStr">
@@ -1243,6 +2122,30 @@
           <t>KRW</t>
         </is>
       </c>
+      <c r="H55" t="n">
+        <v>13</v>
+      </c>
+      <c r="I55" t="n">
+        <v>14</v>
+      </c>
+      <c r="J55" t="n">
+        <v>15</v>
+      </c>
+      <c r="K55" t="n">
+        <v>16</v>
+      </c>
+      <c r="L55" t="n">
+        <v>17</v>
+      </c>
+      <c r="M55" t="n">
+        <v>18</v>
+      </c>
+      <c r="N55" t="n">
+        <v>19</v>
+      </c>
+      <c r="R55" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="56">
       <c r="B56" t="inlineStr">
@@ -1260,6 +2163,30 @@
           <t>CNY</t>
         </is>
       </c>
+      <c r="H56" t="n">
+        <v>14</v>
+      </c>
+      <c r="I56" t="n">
+        <v>15</v>
+      </c>
+      <c r="J56" t="n">
+        <v>16</v>
+      </c>
+      <c r="K56" t="n">
+        <v>17</v>
+      </c>
+      <c r="L56" t="n">
+        <v>18</v>
+      </c>
+      <c r="M56" t="n">
+        <v>19</v>
+      </c>
+      <c r="N56" t="n">
+        <v>20</v>
+      </c>
+      <c r="R56" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="57">
       <c r="B57" t="inlineStr">
@@ -1272,15 +2199,34 @@
           <t>Other</t>
         </is>
       </c>
-    </row>
-    <row r="58"/>
-    <row r="59"/>
-    <row r="60"/>
-    <row r="61"/>
-    <row r="62"/>
-    <row r="63"/>
-    <row r="64"/>
-    <row r="65"/>
+      <c r="G57" t="n">
+        <v>14</v>
+      </c>
+      <c r="H57" t="n">
+        <v>15</v>
+      </c>
+      <c r="I57" t="n">
+        <v>16</v>
+      </c>
+      <c r="J57" t="n">
+        <v>17</v>
+      </c>
+      <c r="K57" t="n">
+        <v>18</v>
+      </c>
+      <c r="L57" t="n">
+        <v>19</v>
+      </c>
+      <c r="M57" t="n">
+        <v>20</v>
+      </c>
+      <c r="N57" t="n">
+        <v>21</v>
+      </c>
+      <c r="R57" t="n">
+        <v>22</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
